--- a/INFORME_INSUMOS/Inventario_INSUMO_INCENDIO_2026-08-17.xlsx
+++ b/INFORME_INSUMOS/Inventario_INSUMO_INCENDIO_2026-08-17.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capas desplegadas'!$A$4:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inventario completo'!$A$4:$I$779</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura por región'!$A$4:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura por región'!$A$4:$M$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Brechas y pendientes'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,12 +571,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,6 +589,8 @@
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -596,11 +600,15 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -614,6 +622,8 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -627,6 +637,8 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -640,6 +652,8 @@
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -649,15 +663,19 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>775 archivos · 832 MB</t>
+          <t>775 archivos · 832 MB · 26 fuentes directas (3.4% de los archivos, 25.6% del peso)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -672,7 +690,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>% ARCHIVOS</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
           <t>MB</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>% MB</t>
         </is>
       </c>
     </row>
@@ -686,7 +714,13 @@
         <v>266</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>16.9</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +733,13 @@
         <v>182</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>93.09999999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="12">
@@ -712,7 +752,13 @@
         <v>88</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>7.4</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +771,13 @@
         <v>85</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>93.2</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="14">
@@ -738,7 +790,13 @@
         <v>81</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>396.2</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>47.7</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +809,13 @@
         <v>34</v>
       </c>
       <c r="C15" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>0.1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -764,7 +828,13 @@
         <v>26</v>
       </c>
       <c r="C16" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>212.8</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>25.6</v>
       </c>
     </row>
     <row r="17">
@@ -777,7 +847,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>7.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +866,13 @@
         <v>2</v>
       </c>
       <c r="C18" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>0.1</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -803,13 +885,21 @@
         <v>2</v>
       </c>
       <c r="C19" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>2.4</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -819,6 +909,8 @@
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -828,10 +920,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>14705 puntos · 9 temporadas · 16 regiones</t>
+          <t>14705 puntos · 9 temporadas · 16 regiones · 98,1% de las 14985 filas leídas (1,9% descartado sin coordenada válida)</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -841,10 +935,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>1863 obras · 4790 km · 15 regiones</t>
+          <t>1863 obras · 4790 km dibujados = 97,8% de los 4899 km planificados · 15 de 16 regiones (93,8%)</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -854,10 +950,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>327 puntos · 7 regiones (faltan 9)</t>
+          <t>327 puntos · 7 de 16 regiones (43,8%) — faltan 9 (56,3%)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -871,6 +969,8 @@
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -884,6 +984,8 @@
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -897,6 +999,8 @@
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31465,23 +31569,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Qué capa cubre cada región (conteos del despliegue vigente)</t>
+          <t>Qué capa cubre cada región (conteos y % del total nacional; avance = reportado/planificado)</t>
         </is>
       </c>
     </row>
@@ -31505,30 +31614,55 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
+          <t>Incendios % país</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
           <t>OECV dibujado (km)</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>OECV % país</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>OECV planificado (km, Excel)</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>OECV reportado (km, Excel)</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Avance OECV %</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>Puntos stand-by (n)</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Puntos % país</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Rutas 25-26 (n)</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>Rutas % país</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Fuente de rutas</t>
         </is>
@@ -31543,16 +31677,25 @@
       <c r="B5" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
-      <c r="D5" s="17" t="n">
+      <c r="C5" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="17" t="inlineStr"/>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="L5" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31568,19 +31711,32 @@
         <v>27</v>
       </c>
       <c r="C6" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>94.2</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="E6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="G6" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="n">
+      <c r="H6" s="17" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr"/>
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="L6" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31596,19 +31752,32 @@
         <v>8</v>
       </c>
       <c r="C7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>2.2</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>2.1</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="n">
+        <v>2.1</v>
+      </c>
       <c r="G7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="L7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31624,17 +31793,28 @@
         <v>65</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>28.7</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>28.7</v>
       </c>
       <c r="E8" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -31650,17 +31830,28 @@
         <v>345</v>
       </c>
       <c r="C9" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="E9" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F9" s="17" t="n">
         <v>42.6</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="G9" s="17" t="n">
         <v>42.9898</v>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="17" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr"/>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="17" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -31676,21 +31867,36 @@
         <v>1212</v>
       </c>
       <c r="C10" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D10" s="17" t="n">
         <v>163</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="E10" s="17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>203</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="G10" s="17" t="n">
         <v>203.9</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="H10" s="17" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="I10" s="17" t="n">
         <v>108</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="J10" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="K10" s="17" t="n">
         <v>311</v>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="L10" s="17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31706,21 +31912,36 @@
         <v>1218</v>
       </c>
       <c r="C11" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D11" s="17" t="n">
         <v>877.6</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="E11" s="17" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F11" s="17" t="n">
         <v>878.8</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="G11" s="17" t="n">
         <v>380.776</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="H11" s="17" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I11" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="J11" s="17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K11" s="17" t="n">
         <v>189</v>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="L11" s="17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31736,21 +31957,36 @@
         <v>1092</v>
       </c>
       <c r="C12" s="17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D12" s="17" t="n">
         <v>836.5</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="E12" s="17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>836.8</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="G12" s="17" t="n">
         <v>745.126</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="H12" s="17" t="n">
+        <v>89</v>
+      </c>
+      <c r="I12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="J12" s="17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" s="17" t="n">
         <v>463</v>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="L12" s="17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31766,19 +32002,32 @@
         <v>1734</v>
       </c>
       <c r="C13" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D13" s="17" t="n">
         <v>496.1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="E13" s="17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>422.2</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="G13" s="17" t="n">
         <v>457.28</v>
       </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="n">
+      <c r="H13" s="17" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="n">
         <v>1288</v>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="L13" s="17" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
@@ -31794,19 +32043,32 @@
         <v>1346</v>
       </c>
       <c r="C14" s="17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D14" s="17" t="n">
         <v>394.5</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="E14" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F14" s="17" t="n">
         <v>394.4</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="G14" s="17" t="n">
         <v>244.2</v>
       </c>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="n">
+      <c r="H14" s="17" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr"/>
+      <c r="J14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="n">
         <v>330</v>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="L14" s="17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
@@ -31822,21 +32084,36 @@
         <v>2820</v>
       </c>
       <c r="C15" s="17" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <v>601</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="E15" s="17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F15" s="17" t="n">
         <v>731.595</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="G15" s="17" t="n">
         <v>734.545</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="H15" s="17" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="I15" s="17" t="n">
         <v>62</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="J15" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" s="17" t="n">
         <v>382</v>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="L15" s="17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
@@ -31852,21 +32129,36 @@
         <v>3370</v>
       </c>
       <c r="C16" s="17" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D16" s="17" t="n">
         <v>694.4</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="E16" s="17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F16" s="17" t="n">
         <v>695.1</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="G16" s="17" t="n">
         <v>435.06</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="H16" s="17" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="I16" s="17" t="n">
         <v>51</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="J16" s="17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K16" s="17" t="n">
         <v>480</v>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="L16" s="17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
@@ -31882,19 +32174,32 @@
         <v>518</v>
       </c>
       <c r="C17" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" s="17" t="n">
         <v>223.3</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="E17" s="17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>223.1</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="G17" s="17" t="n">
         <v>244.528</v>
       </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="n">
+      <c r="H17" s="17" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr"/>
+      <c r="J17" s="17" t="inlineStr"/>
+      <c r="K17" s="17" t="n">
         <v>142</v>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="L17" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31910,21 +32215,36 @@
         <v>662</v>
       </c>
       <c r="C18" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" s="17" t="n">
         <v>260.5</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="E18" s="17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F18" s="17" t="n">
         <v>317.8</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="G18" s="17" t="n">
         <v>261.9</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="H18" s="17" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="I18" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="J18" s="17" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K18" s="17" t="n">
         <v>203</v>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="L18" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
@@ -31940,21 +32260,36 @@
         <v>177</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>46</v>
+        <v>1.2</v>
       </c>
       <c r="D19" s="17" t="n">
         <v>46</v>
       </c>
       <c r="E19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="G19" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="J19" s="17" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K19" s="17" t="n">
         <v>95</v>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="L19" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31970,19 +32305,32 @@
         <v>92</v>
       </c>
       <c r="C20" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D20" s="17" t="n">
         <v>7.4</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="E20" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F20" s="17" t="n">
         <v>52.4</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="G20" s="17" t="n">
         <v>40.983</v>
       </c>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="n">
+      <c r="H20" s="17" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="n">
         <v>58</v>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="L20" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
@@ -31999,17 +32347,65 @@
       <c r="D21" s="17" t="inlineStr"/>
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="17" t="inlineStr"/>
+      <c r="J21" s="17" t="inlineStr"/>
+      <c r="K21" s="17" t="n">
         <v>1277</v>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="L21" s="17" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL PAÍS</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>14705</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>4789.8</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>4898.595</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>3860.288</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>327</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>5278</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H21"/>
+  <autoFilter ref="A4:M22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
